--- a/data/nzd0500/nzd0500.xlsx
+++ b/data/nzd0500/nzd0500.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M540"/>
+  <dimension ref="A1:M544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24748,6 +24748,186 @@
         <v>368.86</v>
       </c>
       <c r="M540" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:10+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>353.2</v>
+      </c>
+      <c r="C541" t="n">
+        <v>353.88</v>
+      </c>
+      <c r="D541" t="n">
+        <v>351.11</v>
+      </c>
+      <c r="E541" t="n">
+        <v>355.99</v>
+      </c>
+      <c r="F541" t="n">
+        <v>354.34</v>
+      </c>
+      <c r="G541" t="n">
+        <v>354.12</v>
+      </c>
+      <c r="H541" t="n">
+        <v>352.84</v>
+      </c>
+      <c r="I541" t="n">
+        <v>355.51</v>
+      </c>
+      <c r="J541" t="n">
+        <v>362.47</v>
+      </c>
+      <c r="K541" t="n">
+        <v>366.01</v>
+      </c>
+      <c r="L541" t="n">
+        <v>368.86</v>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>354.75</v>
+      </c>
+      <c r="C542" t="n">
+        <v>354.91</v>
+      </c>
+      <c r="D542" t="n">
+        <v>352.15</v>
+      </c>
+      <c r="E542" t="n">
+        <v>356.75</v>
+      </c>
+      <c r="F542" t="n">
+        <v>355.07</v>
+      </c>
+      <c r="G542" t="n">
+        <v>355.22</v>
+      </c>
+      <c r="H542" t="n">
+        <v>353.85</v>
+      </c>
+      <c r="I542" t="n">
+        <v>356.9</v>
+      </c>
+      <c r="J542" t="n">
+        <v>364.44</v>
+      </c>
+      <c r="K542" t="n">
+        <v>367.67</v>
+      </c>
+      <c r="L542" t="n">
+        <v>371.24</v>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>354.91</v>
+      </c>
+      <c r="C543" t="n">
+        <v>355.08</v>
+      </c>
+      <c r="D543" t="n">
+        <v>352.24</v>
+      </c>
+      <c r="E543" t="n">
+        <v>356.82</v>
+      </c>
+      <c r="F543" t="n">
+        <v>355.1</v>
+      </c>
+      <c r="G543" t="n">
+        <v>355.59</v>
+      </c>
+      <c r="H543" t="n">
+        <v>354.18</v>
+      </c>
+      <c r="I543" t="n">
+        <v>357.48</v>
+      </c>
+      <c r="J543" t="n">
+        <v>364.89</v>
+      </c>
+      <c r="K543" t="n">
+        <v>367.81</v>
+      </c>
+      <c r="L543" t="n">
+        <v>371.52</v>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>355.7</v>
+      </c>
+      <c r="C544" t="n">
+        <v>355.25</v>
+      </c>
+      <c r="D544" t="n">
+        <v>352.33</v>
+      </c>
+      <c r="E544" t="n">
+        <v>356.9</v>
+      </c>
+      <c r="F544" t="n">
+        <v>355.25</v>
+      </c>
+      <c r="G544" t="n">
+        <v>355.99</v>
+      </c>
+      <c r="H544" t="n">
+        <v>354.55</v>
+      </c>
+      <c r="I544" t="n">
+        <v>358.11</v>
+      </c>
+      <c r="J544" t="n">
+        <v>364.75</v>
+      </c>
+      <c r="K544" t="n">
+        <v>367.93</v>
+      </c>
+      <c r="L544" t="n">
+        <v>371.64</v>
+      </c>
+      <c r="M544" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24764,7 +24944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B633"/>
+  <dimension ref="A1:B638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31097,6 +31277,56 @@
       </c>
       <c r="B633" t="n">
         <v>0.46</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>
@@ -31265,28 +31495,28 @@
         <v>0.0761</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4316123231377244</v>
+        <v>-0.4440698686622133</v>
       </c>
       <c r="J2" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K2" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1540726296811264</v>
+        <v>0.1622048851787742</v>
       </c>
       <c r="M2" t="n">
-        <v>5.621591195464429</v>
+        <v>5.657434699535902</v>
       </c>
       <c r="N2" t="n">
-        <v>50.71730317266314</v>
+        <v>50.87440908951157</v>
       </c>
       <c r="O2" t="n">
-        <v>7.121608187246975</v>
+        <v>7.132629885919469</v>
       </c>
       <c r="P2" t="n">
-        <v>374.772133967087</v>
+        <v>374.9207735357689</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31343,28 +31573,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3846283578293235</v>
+        <v>-0.3985192339439876</v>
       </c>
       <c r="J3" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K3" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1296980560845339</v>
+        <v>0.1380832752188397</v>
       </c>
       <c r="M3" t="n">
-        <v>5.519854631250619</v>
+        <v>5.55158650083117</v>
       </c>
       <c r="N3" t="n">
-        <v>49.22434962815392</v>
+        <v>49.516013631254</v>
       </c>
       <c r="O3" t="n">
-        <v>7.016006672470739</v>
+        <v>7.036761586927185</v>
       </c>
       <c r="P3" t="n">
-        <v>374.6328451838249</v>
+        <v>374.7985929443459</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31421,28 +31651,28 @@
         <v>0.1015</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4248478263855179</v>
+        <v>-0.4373851857802877</v>
       </c>
       <c r="J4" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K4" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1674776606853076</v>
+        <v>0.1761333119937333</v>
       </c>
       <c r="M4" t="n">
-        <v>5.062045156649354</v>
+        <v>5.089174047754869</v>
       </c>
       <c r="N4" t="n">
-        <v>44.49044092450894</v>
+        <v>44.69577294582153</v>
       </c>
       <c r="O4" t="n">
-        <v>6.670115510582177</v>
+        <v>6.6854897311881</v>
       </c>
       <c r="P4" t="n">
-        <v>371.9643860412583</v>
+        <v>372.1139834649564</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31499,28 +31729,28 @@
         <v>0.0692</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4221543083576042</v>
+        <v>-0.4271484227308954</v>
       </c>
       <c r="J5" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K5" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2039812561893454</v>
+        <v>0.2098403631036688</v>
       </c>
       <c r="M5" t="n">
-        <v>4.468975785664935</v>
+        <v>4.460061969949888</v>
       </c>
       <c r="N5" t="n">
-        <v>34.48548853040494</v>
+        <v>34.31676163108182</v>
       </c>
       <c r="O5" t="n">
-        <v>5.87243463398316</v>
+        <v>5.858051009600532</v>
       </c>
       <c r="P5" t="n">
-        <v>371.381629618267</v>
+        <v>371.4412178261753</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31577,28 +31807,28 @@
         <v>0.0794</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4036540777981009</v>
+        <v>-0.4083100349995858</v>
       </c>
       <c r="J6" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K6" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1827628878864491</v>
+        <v>0.1881316960322634</v>
       </c>
       <c r="M6" t="n">
-        <v>4.619947308671454</v>
+        <v>4.603922602559345</v>
       </c>
       <c r="N6" t="n">
-        <v>36.12764524453947</v>
+        <v>35.93574021149096</v>
       </c>
       <c r="O6" t="n">
-        <v>6.010627691392927</v>
+        <v>5.994642625836086</v>
       </c>
       <c r="P6" t="n">
-        <v>368.9777290402023</v>
+        <v>369.0332822833888</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31655,28 +31885,28 @@
         <v>0.134</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3535874495516651</v>
+        <v>-0.356126626352356</v>
       </c>
       <c r="J7" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K7" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="L7" t="n">
-        <v>0.156093959895704</v>
+        <v>0.1598476419677413</v>
       </c>
       <c r="M7" t="n">
-        <v>4.657991574907131</v>
+        <v>4.635833093846855</v>
       </c>
       <c r="N7" t="n">
-        <v>33.51680238640356</v>
+        <v>33.29534962144285</v>
       </c>
       <c r="O7" t="n">
-        <v>5.789369774543993</v>
+        <v>5.770212268317592</v>
       </c>
       <c r="P7" t="n">
-        <v>366.4736177894819</v>
+        <v>366.5039073600228</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31733,28 +31963,28 @@
         <v>0.1151</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3792247532341144</v>
+        <v>-0.3836652159535011</v>
       </c>
       <c r="J8" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K8" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1744206627134008</v>
+        <v>0.1796475732468159</v>
       </c>
       <c r="M8" t="n">
-        <v>4.63229132702996</v>
+        <v>4.618683176922182</v>
       </c>
       <c r="N8" t="n">
-        <v>33.75321425144472</v>
+        <v>33.57429001724709</v>
       </c>
       <c r="O8" t="n">
-        <v>5.809751651443005</v>
+        <v>5.794332577376543</v>
       </c>
       <c r="P8" t="n">
-        <v>367.0895594835189</v>
+        <v>367.1425372478746</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31811,28 +32041,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2529149785797236</v>
+        <v>-0.2564169687344056</v>
       </c>
       <c r="J9" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K9" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08669268806242636</v>
+        <v>0.08997162379281587</v>
       </c>
       <c r="M9" t="n">
-        <v>4.693774484622535</v>
+        <v>4.679867153084627</v>
       </c>
       <c r="N9" t="n">
-        <v>33.41523082373804</v>
+        <v>33.21741033849187</v>
       </c>
       <c r="O9" t="n">
-        <v>5.78059087150596</v>
+        <v>5.76345472251599</v>
       </c>
       <c r="P9" t="n">
-        <v>366.1965365905747</v>
+        <v>366.2383115256233</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31889,28 +32119,28 @@
         <v>0.1027</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1124786227504435</v>
+        <v>-0.1092251912618935</v>
       </c>
       <c r="J10" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K10" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01832576937148811</v>
+        <v>0.01752820468061445</v>
       </c>
       <c r="M10" t="n">
-        <v>4.644359611092201</v>
+        <v>4.625407804138815</v>
       </c>
       <c r="N10" t="n">
-        <v>33.60516659477851</v>
+        <v>33.40036056919578</v>
       </c>
       <c r="O10" t="n">
-        <v>5.796996342484486</v>
+        <v>5.779304505664655</v>
       </c>
       <c r="P10" t="n">
-        <v>364.9348058338977</v>
+        <v>364.8959709440292</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31967,28 +32197,28 @@
         <v>0.0915</v>
       </c>
       <c r="I11" t="n">
-        <v>0.003989329011720989</v>
+        <v>0.007046344282300703</v>
       </c>
       <c r="J11" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K11" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="L11" t="n">
-        <v>2.41158209022263e-05</v>
+        <v>7.626038538111057e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.574743662370562</v>
+        <v>4.554804019970396</v>
       </c>
       <c r="N11" t="n">
-        <v>32.72262128220069</v>
+        <v>32.51759915536341</v>
       </c>
       <c r="O11" t="n">
-        <v>5.720368981298383</v>
+        <v>5.702420464624072</v>
       </c>
       <c r="P11" t="n">
-        <v>365.155022327489</v>
+        <v>365.1185339121747</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32045,28 +32275,28 @@
         <v>0.0491</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02712260266806861</v>
+        <v>0.02960911853972543</v>
       </c>
       <c r="J12" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K12" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001165075527816306</v>
+        <v>0.001407294839656736</v>
       </c>
       <c r="M12" t="n">
-        <v>4.581102200390484</v>
+        <v>4.559413877213807</v>
       </c>
       <c r="N12" t="n">
-        <v>31.27254754405591</v>
+        <v>31.07256628898848</v>
       </c>
       <c r="O12" t="n">
-        <v>5.592186293754519</v>
+        <v>5.574277198793443</v>
       </c>
       <c r="P12" t="n">
-        <v>368.3845229474786</v>
+        <v>368.3548373923382</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32104,7 +32334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M540"/>
+  <dimension ref="A1:M544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68287,6 +68517,274 @@
         </is>
       </c>
     </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:10+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>-45.7600764871041,170.67816528354112</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>-45.76035930297001,170.67895448501517</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>-45.76060473877865,170.6797712831483</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>-45.76081575308768,170.68060785945192</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>-45.761019723174556,170.68143045485814</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>-45.76117849012021,170.68229311056172</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>-45.761348722955724,170.68315261696176</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>-45.76144854994383,170.68402537495027</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>-45.76145689436283,170.68491379840466</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>-45.76146619665604,170.6857988678789</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>-45.761454069092615,170.68669074875393</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>-45.760064286532995,170.67817493353797</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>-45.76035094548225,170.678960205118</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>-45.7605961683611,170.679776648124</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>-45.760809425691214,170.68061156296008</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>-45.76101346287544,170.6814332928824</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>-45.76116897082725,170.6822969787431</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>-45.761339919967575,170.6831558379787</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>-45.76143624453773,170.68402856239015</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>-45.76143928061257,170.68491662298337</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>-45.761451292747665,170.68580024950597</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>-45.76143267485904,170.68669203593666</t>
+        </is>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>-45.76006302711916,170.67817592966645</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>-45.76034956609103,170.67896114921248</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>-45.760595426690344,170.67977711240067</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>-45.7608088429047,170.68061190407263</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>-45.761013205602865,170.6814334095135</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>-45.76116576888321,170.68229827985834</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>-45.761337043743715,170.6831568903899</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>-45.7614311099078,170.6840298924006</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>-45.76143525716707,170.68491726819144</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>-45.76145003579154,170.6858003660287</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>-45.76143015789036,170.68669218736989</t>
+        </is>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>-45.76005680876317,170.67818084805006</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>-45.76034818669981,170.6789620933069</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>-45.760594685019555,170.6797775766773</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>-45.76080817686296,170.68061229391554</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>-45.76101191924003,170.6814339926691</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>-45.76116230732208,170.68229968646926</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>-45.76133381888663,170.683158070366</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>-45.76142553263733,170.6840313370668</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>-45.76143650890567,170.68491706746008</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>-45.761448958400564,170.68580046590532</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>-45.76142907918951,170.68669225226978</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0500/nzd0500.xlsx
+++ b/data/nzd0500/nzd0500.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M544"/>
+  <dimension ref="A1:M547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24928,6 +24928,141 @@
         <v>371.64</v>
       </c>
       <c r="M544" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>355.7</v>
+      </c>
+      <c r="C545" t="n">
+        <v>355.25</v>
+      </c>
+      <c r="D545" t="n">
+        <v>352.33</v>
+      </c>
+      <c r="E545" t="n">
+        <v>356.9</v>
+      </c>
+      <c r="F545" t="n">
+        <v>355.25</v>
+      </c>
+      <c r="G545" t="n">
+        <v>355.99</v>
+      </c>
+      <c r="H545" t="n">
+        <v>354.55</v>
+      </c>
+      <c r="I545" t="n">
+        <v>358.96</v>
+      </c>
+      <c r="J545" t="n">
+        <v>365.09</v>
+      </c>
+      <c r="K545" t="n">
+        <v>368.05</v>
+      </c>
+      <c r="L545" t="n">
+        <v>371.69</v>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>355.97</v>
+      </c>
+      <c r="C546" t="n">
+        <v>355.93</v>
+      </c>
+      <c r="D546" t="n">
+        <v>352.71</v>
+      </c>
+      <c r="E546" t="n">
+        <v>356.78</v>
+      </c>
+      <c r="F546" t="n">
+        <v>355.66</v>
+      </c>
+      <c r="G546" t="n">
+        <v>356.02</v>
+      </c>
+      <c r="H546" t="n">
+        <v>355.1</v>
+      </c>
+      <c r="I546" t="n">
+        <v>358.98</v>
+      </c>
+      <c r="J546" t="n">
+        <v>365.21</v>
+      </c>
+      <c r="K546" t="n">
+        <v>367.96</v>
+      </c>
+      <c r="L546" t="n">
+        <v>371.73</v>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>355.98</v>
+      </c>
+      <c r="C547" t="n">
+        <v>356.43</v>
+      </c>
+      <c r="D547" t="n">
+        <v>352.82</v>
+      </c>
+      <c r="E547" t="n">
+        <v>356.72</v>
+      </c>
+      <c r="F547" t="n">
+        <v>355.79</v>
+      </c>
+      <c r="G547" t="n">
+        <v>355.86</v>
+      </c>
+      <c r="H547" t="n">
+        <v>355.46</v>
+      </c>
+      <c r="I547" t="n">
+        <v>358.97</v>
+      </c>
+      <c r="J547" t="n">
+        <v>364.89</v>
+      </c>
+      <c r="K547" t="n">
+        <v>367.84</v>
+      </c>
+      <c r="L547" t="n">
+        <v>371.66</v>
+      </c>
+      <c r="M547" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24944,7 +25079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B638"/>
+  <dimension ref="A1:B642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31327,6 +31462,46 @@
       </c>
       <c r="B638" t="n">
         <v>-0.05</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -31495,28 +31670,28 @@
         <v>0.0761</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4440698686622133</v>
+        <v>-0.451748345344768</v>
       </c>
       <c r="J2" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="K2" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1622048851787742</v>
+        <v>0.1676992630255547</v>
       </c>
       <c r="M2" t="n">
-        <v>5.657434699535902</v>
+        <v>5.673614144286705</v>
       </c>
       <c r="N2" t="n">
-        <v>50.87440908951157</v>
+        <v>50.86462048491465</v>
       </c>
       <c r="O2" t="n">
-        <v>7.132629885919469</v>
+        <v>7.131943668097404</v>
       </c>
       <c r="P2" t="n">
-        <v>374.9207735357689</v>
+        <v>375.0127450426035</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31573,28 +31748,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3985192339439876</v>
+        <v>-0.4074100951045386</v>
       </c>
       <c r="J3" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="K3" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1380832752188397</v>
+        <v>0.1438601102120615</v>
       </c>
       <c r="M3" t="n">
-        <v>5.55158650083117</v>
+        <v>5.56778313287912</v>
       </c>
       <c r="N3" t="n">
-        <v>49.516013631254</v>
+        <v>49.60682803001376</v>
       </c>
       <c r="O3" t="n">
-        <v>7.036761586927185</v>
+        <v>7.043211485537954</v>
       </c>
       <c r="P3" t="n">
-        <v>374.7985929443459</v>
+        <v>374.9050829308164</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31651,28 +31826,28 @@
         <v>0.1015</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4373851857802877</v>
+        <v>-0.4457542611838368</v>
       </c>
       <c r="J4" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="K4" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1761333119937333</v>
+        <v>0.182257856511746</v>
       </c>
       <c r="M4" t="n">
-        <v>5.089174047754869</v>
+        <v>5.104264428362305</v>
       </c>
       <c r="N4" t="n">
-        <v>44.69577294582153</v>
+        <v>44.77078108273468</v>
       </c>
       <c r="O4" t="n">
-        <v>6.6854897311881</v>
+        <v>6.691097150896456</v>
       </c>
       <c r="P4" t="n">
-        <v>372.1139834649564</v>
+        <v>372.2142261395305</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31729,28 +31904,28 @@
         <v>0.0692</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4271484227308954</v>
+        <v>-0.4305441779241061</v>
       </c>
       <c r="J5" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="K5" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2098403631036688</v>
+        <v>0.2140517194303271</v>
       </c>
       <c r="M5" t="n">
-        <v>4.460061969949888</v>
+        <v>4.451898871394137</v>
       </c>
       <c r="N5" t="n">
-        <v>34.31676163108182</v>
+        <v>34.1809580529284</v>
       </c>
       <c r="O5" t="n">
-        <v>5.858051009600532</v>
+        <v>5.846448328081622</v>
       </c>
       <c r="P5" t="n">
-        <v>371.4412178261753</v>
+        <v>371.4818929783514</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31807,28 +31982,28 @@
         <v>0.0794</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4083100349995858</v>
+        <v>-0.4109773570261894</v>
       </c>
       <c r="J6" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="K6" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1881316960322634</v>
+        <v>0.1916738774902299</v>
       </c>
       <c r="M6" t="n">
-        <v>4.603922602559345</v>
+        <v>4.58878814120331</v>
       </c>
       <c r="N6" t="n">
-        <v>35.93574021149096</v>
+        <v>35.7711594835204</v>
       </c>
       <c r="O6" t="n">
-        <v>5.994642625836086</v>
+        <v>5.980899554709175</v>
       </c>
       <c r="P6" t="n">
-        <v>369.0332822833888</v>
+        <v>369.0652289153819</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31885,28 +32060,28 @@
         <v>0.134</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.356126626352356</v>
+        <v>-0.3571502496497371</v>
       </c>
       <c r="J7" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="K7" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1598476419677413</v>
+        <v>0.1620783337840909</v>
       </c>
       <c r="M7" t="n">
-        <v>4.635833093846855</v>
+        <v>4.615200553060864</v>
       </c>
       <c r="N7" t="n">
-        <v>33.29534962144285</v>
+        <v>33.11722320634988</v>
       </c>
       <c r="O7" t="n">
-        <v>5.770212268317592</v>
+        <v>5.754756572293036</v>
       </c>
       <c r="P7" t="n">
-        <v>366.5039073600228</v>
+        <v>366.5161685745208</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31963,28 +32138,28 @@
         <v>0.1151</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3836652159535011</v>
+        <v>-0.3855774059068374</v>
       </c>
       <c r="J8" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="K8" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1796475732468159</v>
+        <v>0.1826648273812075</v>
       </c>
       <c r="M8" t="n">
-        <v>4.618683176922182</v>
+        <v>4.602099213315378</v>
       </c>
       <c r="N8" t="n">
-        <v>33.57429001724709</v>
+        <v>33.40734439732557</v>
       </c>
       <c r="O8" t="n">
-        <v>5.794332577376543</v>
+        <v>5.779908684168424</v>
       </c>
       <c r="P8" t="n">
-        <v>367.1425372478746</v>
+        <v>367.1654375491209</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32041,28 +32216,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2564169687344056</v>
+        <v>-0.2567985080551151</v>
       </c>
       <c r="J9" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="K9" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08997162379281587</v>
+        <v>0.09111421247621532</v>
       </c>
       <c r="M9" t="n">
-        <v>4.679867153084627</v>
+        <v>4.656379910352942</v>
       </c>
       <c r="N9" t="n">
-        <v>33.21741033849187</v>
+        <v>33.03556366403615</v>
       </c>
       <c r="O9" t="n">
-        <v>5.76345472251599</v>
+        <v>5.747657232650199</v>
       </c>
       <c r="P9" t="n">
-        <v>366.2383115256233</v>
+        <v>366.2428814888178</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32119,28 +32294,28 @@
         <v>0.1027</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1092251912618935</v>
+        <v>-0.1058391460893742</v>
       </c>
       <c r="J10" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="K10" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01752820468061445</v>
+        <v>0.01662797975850139</v>
       </c>
       <c r="M10" t="n">
-        <v>4.625407804138815</v>
+        <v>4.61593413460629</v>
       </c>
       <c r="N10" t="n">
-        <v>33.40036056919578</v>
+        <v>33.26936846403687</v>
       </c>
       <c r="O10" t="n">
-        <v>5.779304505664655</v>
+        <v>5.767960511657208</v>
       </c>
       <c r="P10" t="n">
-        <v>364.8959709440292</v>
+        <v>364.8554130272108</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32197,28 +32372,28 @@
         <v>0.0915</v>
       </c>
       <c r="I11" t="n">
-        <v>0.007046344282300703</v>
+        <v>0.009921036075322362</v>
       </c>
       <c r="J11" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="K11" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="L11" t="n">
-        <v>7.626038538111057e-05</v>
+        <v>0.0001526468390331548</v>
       </c>
       <c r="M11" t="n">
-        <v>4.554804019970396</v>
+        <v>4.542786085600318</v>
       </c>
       <c r="N11" t="n">
-        <v>32.51759915536341</v>
+        <v>32.37676743855301</v>
       </c>
       <c r="O11" t="n">
-        <v>5.702420464624072</v>
+        <v>5.690058649834201</v>
       </c>
       <c r="P11" t="n">
-        <v>365.1185339121747</v>
+        <v>365.0841015820209</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32275,28 +32450,28 @@
         <v>0.0491</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02960911853972543</v>
+        <v>0.03237550062833198</v>
       </c>
       <c r="J12" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="K12" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001407294839656736</v>
+        <v>0.00169860455318549</v>
       </c>
       <c r="M12" t="n">
-        <v>4.559413877213807</v>
+        <v>4.546582387456035</v>
       </c>
       <c r="N12" t="n">
-        <v>31.07256628898848</v>
+        <v>30.93683791890834</v>
       </c>
       <c r="O12" t="n">
-        <v>5.574277198793443</v>
+        <v>5.562089348339196</v>
       </c>
       <c r="P12" t="n">
-        <v>368.3548373923382</v>
+        <v>368.3217015737368</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32334,7 +32509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M544"/>
+  <dimension ref="A1:M547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68785,6 +68960,207 @@
         </is>
       </c>
     </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>-45.76005680876317,170.67818084805006</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>-45.76034818669981,170.6789620933069</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>-45.760594685019555,170.6797775766773</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>-45.76080817686296,170.68061229391554</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>-45.76101191924003,170.6814339926691</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>-45.76116230732208,170.68229968646926</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>-45.76133381888663,170.683158070366</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>-45.76141800774855,170.68403328621915</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>-45.76143346896906,170.68491755495054</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>-45.761447881009616,170.68580056578193</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>-45.76142862973083,170.68669227931142</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>-45.76005468350219,170.67818252901637</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>-45.7603426691348,170.6789658696841</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>-45.76059155352075,170.67977953695637</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>-45.760809175925566,170.68061170915118</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>-45.76100840318157,170.68143558662752</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>-45.76116204770499,170.68229979196505</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>-45.7613290251801,170.68315982438423</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>-45.76141783069236,170.68403333208155</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>-45.76143239605025,170.684917727006</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>-45.76144868905283,170.68580049087447</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>-45.761428270163876,170.68669230094474</t>
+        </is>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>-45.760054604788834,170.67818259127438</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>-45.760338612101634,170.67896864643157</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>-45.760590647034235,170.67978010440555</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>-45.760809675456876,170.68061141676898</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>-45.76100728833376,170.68143609202892</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>-45.76116343232945,170.68229922932073</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>-45.76132588748128,170.68316097246876</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>-45.761417919220456,170.68403330915035</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>-45.76143525716707,170.68491726819144</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>-45.7614497664438,170.68580039099785</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>-45.761428899406035,170.68669226308643</t>
+        </is>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0500/nzd0500.xlsx
+++ b/data/nzd0500/nzd0500.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M547"/>
+  <dimension ref="A1:M548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25063,6 +25063,51 @@
         <v>371.66</v>
       </c>
       <c r="M547" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>357.18</v>
+      </c>
+      <c r="C548" t="n">
+        <v>357.38</v>
+      </c>
+      <c r="D548" t="n">
+        <v>353.55</v>
+      </c>
+      <c r="E548" t="n">
+        <v>357.55</v>
+      </c>
+      <c r="F548" t="n">
+        <v>356.46</v>
+      </c>
+      <c r="G548" t="n">
+        <v>356.54</v>
+      </c>
+      <c r="H548" t="n">
+        <v>356</v>
+      </c>
+      <c r="I548" t="n">
+        <v>359.88</v>
+      </c>
+      <c r="J548" t="n">
+        <v>365.65</v>
+      </c>
+      <c r="K548" t="n">
+        <v>368.62</v>
+      </c>
+      <c r="L548" t="n">
+        <v>372.55</v>
+      </c>
+      <c r="M548" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25079,7 +25124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B642"/>
+  <dimension ref="A1:B643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31502,6 +31547,16 @@
       </c>
       <c r="B642" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -31670,28 +31725,28 @@
         <v>0.0761</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.451748345344768</v>
+        <v>-0.4537876881923585</v>
       </c>
       <c r="J2" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K2" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1676992630255547</v>
+        <v>0.1693173629725686</v>
       </c>
       <c r="M2" t="n">
-        <v>5.673614144286705</v>
+        <v>5.675771814783673</v>
       </c>
       <c r="N2" t="n">
-        <v>50.86462048491465</v>
+        <v>50.82865502925165</v>
       </c>
       <c r="O2" t="n">
-        <v>7.131943668097404</v>
+        <v>7.129421787862719</v>
       </c>
       <c r="P2" t="n">
-        <v>375.0127450426035</v>
+        <v>375.0372782266865</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31748,28 +31803,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4074100951045386</v>
+        <v>-0.4097763190527811</v>
       </c>
       <c r="J3" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K3" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1438601102120615</v>
+        <v>0.1455551987417496</v>
       </c>
       <c r="M3" t="n">
-        <v>5.56778313287912</v>
+        <v>5.570208239727078</v>
       </c>
       <c r="N3" t="n">
-        <v>49.60682803001376</v>
+        <v>49.59290715468415</v>
       </c>
       <c r="O3" t="n">
-        <v>7.043211485537954</v>
+        <v>7.042223168480544</v>
       </c>
       <c r="P3" t="n">
-        <v>374.9050829308164</v>
+        <v>374.9335484768487</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31826,28 +31881,28 @@
         <v>0.1015</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4457542611838368</v>
+        <v>-0.4481560849544476</v>
       </c>
       <c r="J4" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K4" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L4" t="n">
-        <v>0.182257856511746</v>
+        <v>0.1841495791100544</v>
       </c>
       <c r="M4" t="n">
-        <v>5.104264428362305</v>
+        <v>5.107190288537984</v>
       </c>
       <c r="N4" t="n">
-        <v>44.77078108273468</v>
+        <v>44.76802856920174</v>
       </c>
       <c r="O4" t="n">
-        <v>6.691097150896456</v>
+        <v>6.69089146296678</v>
       </c>
       <c r="P4" t="n">
-        <v>372.2142261395305</v>
+        <v>372.2431199494992</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31904,28 +31959,28 @@
         <v>0.0692</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4305441779241061</v>
+        <v>-0.4313721169091571</v>
       </c>
       <c r="J5" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K5" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2140517194303271</v>
+        <v>0.2152704983637291</v>
       </c>
       <c r="M5" t="n">
-        <v>4.451898871394137</v>
+        <v>4.447750040706968</v>
       </c>
       <c r="N5" t="n">
-        <v>34.1809580529284</v>
+        <v>34.1278686595897</v>
       </c>
       <c r="O5" t="n">
-        <v>5.846448328081622</v>
+        <v>5.841906252208238</v>
       </c>
       <c r="P5" t="n">
-        <v>371.4818929783514</v>
+        <v>371.4918530395316</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31982,28 +32037,28 @@
         <v>0.0794</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4109773570261894</v>
+        <v>-0.4115160442969656</v>
       </c>
       <c r="J6" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K6" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1916738774902299</v>
+        <v>0.192631814377261</v>
       </c>
       <c r="M6" t="n">
-        <v>4.58878814120331</v>
+        <v>4.582433356881038</v>
       </c>
       <c r="N6" t="n">
-        <v>35.7711594835204</v>
+        <v>35.7097430190781</v>
       </c>
       <c r="O6" t="n">
-        <v>5.980899554709175</v>
+        <v>5.975762965436137</v>
       </c>
       <c r="P6" t="n">
-        <v>369.0652289153819</v>
+        <v>369.0717092940944</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32060,28 +32115,28 @@
         <v>0.134</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3571502496497371</v>
+        <v>-0.3572618004947408</v>
       </c>
       <c r="J7" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K7" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1620783337840909</v>
+        <v>0.1626607294233153</v>
       </c>
       <c r="M7" t="n">
-        <v>4.615200553060864</v>
+        <v>4.607285836036606</v>
       </c>
       <c r="N7" t="n">
-        <v>33.11722320634988</v>
+        <v>33.0568504505819</v>
       </c>
       <c r="O7" t="n">
-        <v>5.754756572293036</v>
+        <v>5.749508713845201</v>
       </c>
       <c r="P7" t="n">
-        <v>366.5161685745208</v>
+        <v>366.5175105251488</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32138,28 +32193,28 @@
         <v>0.1151</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3855774059068374</v>
+        <v>-0.3858427990325314</v>
       </c>
       <c r="J8" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K8" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1826648273812075</v>
+        <v>0.1834139869936059</v>
       </c>
       <c r="M8" t="n">
-        <v>4.602099213315378</v>
+        <v>4.594895097854272</v>
       </c>
       <c r="N8" t="n">
-        <v>33.40734439732557</v>
+        <v>33.34723635442327</v>
       </c>
       <c r="O8" t="n">
-        <v>5.779908684168424</v>
+        <v>5.774706603319625</v>
       </c>
       <c r="P8" t="n">
-        <v>367.1654375491209</v>
+        <v>367.1686302140593</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32216,28 +32271,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2567985080551151</v>
+        <v>-0.2565832087866354</v>
       </c>
       <c r="J9" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K9" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09111421247621532</v>
+        <v>0.09127714938169929</v>
       </c>
       <c r="M9" t="n">
-        <v>4.656379910352942</v>
+        <v>4.648773986525171</v>
       </c>
       <c r="N9" t="n">
-        <v>33.03556366403615</v>
+        <v>32.97580513649307</v>
       </c>
       <c r="O9" t="n">
-        <v>5.747657232650199</v>
+        <v>5.742456367835377</v>
       </c>
       <c r="P9" t="n">
-        <v>366.2428814888178</v>
+        <v>366.2402914502704</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32294,28 +32349,28 @@
         <v>0.1027</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1058391460893742</v>
+        <v>-0.1045071812788081</v>
       </c>
       <c r="J10" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K10" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01662797975850139</v>
+        <v>0.0162656636429831</v>
       </c>
       <c r="M10" t="n">
-        <v>4.61593413460629</v>
+        <v>4.613685462694868</v>
       </c>
       <c r="N10" t="n">
-        <v>33.26936846403687</v>
+        <v>33.23287202373086</v>
       </c>
       <c r="O10" t="n">
-        <v>5.767960511657208</v>
+        <v>5.764795922123424</v>
       </c>
       <c r="P10" t="n">
-        <v>364.8554130272108</v>
+        <v>364.8393895626284</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32372,28 +32427,28 @@
         <v>0.0915</v>
       </c>
       <c r="I11" t="n">
-        <v>0.009921036075322362</v>
+        <v>0.0111108269577756</v>
       </c>
       <c r="J11" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K11" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0001526468390331548</v>
+        <v>0.0001920345495822762</v>
       </c>
       <c r="M11" t="n">
-        <v>4.542786085600318</v>
+        <v>4.539805893679404</v>
       </c>
       <c r="N11" t="n">
-        <v>32.37676743855301</v>
+        <v>32.33698703897643</v>
       </c>
       <c r="O11" t="n">
-        <v>5.690058649834201</v>
+        <v>5.686561970028677</v>
       </c>
       <c r="P11" t="n">
-        <v>365.0841015820209</v>
+        <v>365.069788462099</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32450,28 +32505,28 @@
         <v>0.0491</v>
       </c>
       <c r="I12" t="n">
-        <v>0.03237550062833198</v>
+        <v>0.03359568451473242</v>
       </c>
       <c r="J12" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K12" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L12" t="n">
-        <v>0.00169860455318549</v>
+        <v>0.001834302495100082</v>
       </c>
       <c r="M12" t="n">
-        <v>4.546582387456035</v>
+        <v>4.543603809301731</v>
       </c>
       <c r="N12" t="n">
-        <v>30.93683791890834</v>
+        <v>30.90069421157104</v>
       </c>
       <c r="O12" t="n">
-        <v>5.562089348339196</v>
+        <v>5.558839286359253</v>
       </c>
       <c r="P12" t="n">
-        <v>368.3217015737368</v>
+        <v>368.3070228276224</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32509,7 +32564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M547"/>
+  <dimension ref="A1:M548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69161,6 +69216,73 @@
         </is>
       </c>
     </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>-45.760045159184195,170.67819006223414</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>-45.760330903738385,170.67897392225063</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>-45.76058463126006,170.679783870204</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>-45.76080276527374,170.68061546138878</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>-45.76100154257961,170.6814386967897</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>-45.76115754767548,170.68230162055897</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>-45.76132118093301,170.68316269459527</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>-45.761409863162996,170.6840353958893</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>-45.761428462014635,170.68491835787594</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>-45.7614427634025,170.68580104019574</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>-45.76142089904134,170.68669274442746</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
